--- a/inquiry_forms/014_remote_teaching_tools_faculty_inquiry_form--inquiry_forms.xlsx
+++ b/inquiry_forms/014_remote_teaching_tools_faculty_inquiry_form--inquiry_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Satisfaction with online courses</t>
+          <t>Do you need help with online courses?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -607,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Are you a new faculty member?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Do you need help with anything else?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>What is your role in the department?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Do you have any other comments or suggestions?</t>
+          <t>Do you teach face-to-face?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Are there any technical issues you are experiencing with our remote teaching tools?</t>
+          <t>Form 9</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Is this form helping you?</t>
+          <t>What is your department?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Do you need help with anything else?</t>
+          <t>Do you have any comments?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Are you a new faculty member?</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +791,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What is your role?</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Do you teach face-to-face?</t>
+          <t>Form 14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Do you need help with anything else?</t>
+          <t>Are you teaching online?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What is your department?</t>
+          <t>Are you a graduate student?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,7 +883,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Do you need help with anything else?</t>
+          <t>Do you have any other comments?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Do you need help with anything else?</t>
+          <t>Form 18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,7 +929,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -939,149 +939,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Are you teaching online?</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>form_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Do you need help with anything else?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>form_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Do you need help with anything else?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>form_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Do you need help with anything else?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>form_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Are you a graduate student?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>form_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What is your role in the department?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>form_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Do you need help with anything else?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +960,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,918 +988,612 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_4_choices</t>
+          <t>form_3_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>choice_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Choice 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_4_choices</t>
+          <t>form_3_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>choice_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Choice 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_4_choices</t>
+          <t>form_3_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>choice_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Choice 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_9_choices</t>
+          <t>form_4_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>choice_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Choice 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>form_9_choices</t>
+          <t>form_4_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>choice_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Choice 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>form_9_choices</t>
+          <t>form_4_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>choice_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Choice 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>form_10_choices</t>
+          <t>form_5_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>choice_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Choice 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>form_10_choices</t>
+          <t>form_5_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>choice_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Choice 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>form_10_choices</t>
+          <t>form_5_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>choice_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Choice 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>form_11_choices</t>
+          <t>form_6_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>choice_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Choice 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>form_11_choices</t>
+          <t>form_6_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>choice_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Choice 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>form_11_choices</t>
+          <t>form_6_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>choice_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Choice 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>form_12_choices</t>
+          <t>form_7_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>choice_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Choice 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>form_12_choices</t>
+          <t>form_7_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>choice_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Choice 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>form_12_choices</t>
+          <t>form_7_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>choice_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Choice 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>form_13_choices</t>
+          <t>form_8_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>choice_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Choice 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>form_13_choices</t>
+          <t>form_8_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>choice_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Choice 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>form_13_choices</t>
+          <t>form_8_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>choice_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Choice 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>form_14_choices</t>
+          <t>form_9_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>choice_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Choice 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>form_14_choices</t>
+          <t>form_9_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>choice_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Choice 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>form_14_choices</t>
+          <t>form_9_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>choice_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Choice 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>form_15_choices</t>
+          <t>form_10_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>choice_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Choice 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>form_15_choices</t>
+          <t>form_10_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>choice_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Choice 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>form_15_choices</t>
+          <t>form_10_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>choice_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Choice 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>form_16_choices</t>
+          <t>form_14_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>choice_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Choice 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>form_16_choices</t>
+          <t>form_14_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>choice_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Choice 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>form_16_choices</t>
+          <t>form_14_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>choice_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Choice 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>form_17_choices</t>
+          <t>form_15_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>choice_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Choice 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>form_17_choices</t>
+          <t>form_15_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>choice_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Choice 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>form_17_choices</t>
+          <t>form_15_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>choice_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Choice 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>form_18_choices</t>
+          <t>form_16_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>choice_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Choice 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>form_18_choices</t>
+          <t>form_16_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>choice_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Choice 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>form_18_choices</t>
+          <t>form_16_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>choice_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Choice 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>form_19_choices</t>
+          <t>form_18_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>choice_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Choice 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>form_19_choices</t>
+          <t>form_18_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>choice_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Choice 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>form_19_choices</t>
+          <t>form_18_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>choice_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Choice 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>form_20_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>choice_1</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Choice 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>form_20_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>choice_2</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Choice 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>form_20_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>choice_3</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Choice 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>form_21_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>choice_1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Choice 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>form_21_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>choice_2</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Choice 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>form_21_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>choice_3</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Choice 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>form_22_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>choice_1</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Choice 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>form_22_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>choice_2</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Choice 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>form_22_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>choice_3</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Choice 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>form_23_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>choice_1</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Choice 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>form_23_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>choice_2</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Choice 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>form_23_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>choice_3</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Choice 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>form_24_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>choice_1</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Choice 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>form_24_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>choice_2</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Choice 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>form_24_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>choice_3</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Choice 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>form_25_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>choice_1</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Choice 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>form_25_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>choice_2</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Choice 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>form_25_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>choice_3</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Choice 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
